--- a/docs/club-pricing-comparison.xlsx
+++ b/docs/club-pricing-comparison.xlsx
@@ -520,7 +520,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>bot.form_schemas in Supabase. The bot does NOT read Freshdesk — its "Fetch Form Options" node reads this mirror. Where this column disagrees with the form, the member is being told the wrong price and nobody has to decide anything: it is a sync bug. Those rows sort to the top of Differences.</t>
+          <t>bot.form_schemas in Supabase. The bot does NOT read Freshdesk — its "Fetch Form Options" node reads this mirror, fed nightly: Freshdesk → 02:00 ticket_taxonomy → 04:00 form_schemas. Where this column disagrees with the form it is usually LAG, not an error: an edit made just after 02:00 is quoted stale for up to about 26 hours. It still matters — for that window members hear a price the form no longer offers, and the bot's own price guard validates against this mirror, so it protects the stale number. If a row is still here after two nights it is not lag: check Bot - Refresh Form Options.</t>
         </is>
       </c>
     </row>
@@ -721,12 +721,12 @@
       </c>
       <c r="G2" s="5" t="inlineStr">
         <is>
-          <t>BOT OUT OF SYNC</t>
+          <t>bot behind the form</t>
         </is>
       </c>
       <c r="H2" s="6" t="inlineStr">
         <is>
-          <t>Bot quotes €69, the form says €74 — resync bot.form_schemas</t>
+          <t>Bot quotes €69, the form says €74. Usually overnight lag — if it is still here after two nights, check Bot - Refresh Form Options</t>
         </is>
       </c>
       <c r="I2" s="7" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="G3" s="5" t="inlineStr">
         <is>
-          <t>BOT OUT OF SYNC</t>
+          <t>bot behind the form</t>
         </is>
       </c>
       <c r="H3" s="6" t="inlineStr">
         <is>
-          <t>Bot quotes €62, the form says €67 — resync bot.form_schemas</t>
+          <t>Bot quotes €62, the form says €67. Usually overnight lag — if it is still here after two nights, check Bot - Refresh Form Options</t>
         </is>
       </c>
       <c r="I3" s="7" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="G4" s="5" t="inlineStr">
         <is>
-          <t>BOT OUT OF SYNC</t>
+          <t>bot behind the form</t>
         </is>
       </c>
       <c r="H4" s="6" t="inlineStr">
         <is>
-          <t>Bot quotes €55, the form says €60 — resync bot.form_schemas</t>
+          <t>Bot quotes €55, the form says €60. Usually overnight lag — if it is still here after two nights, check Bot - Refresh Form Options</t>
         </is>
       </c>
       <c r="I4" s="7" t="inlineStr">
@@ -20220,12 +20220,12 @@
       </c>
       <c r="G270" s="5" t="inlineStr">
         <is>
-          <t>BOT OUT OF SYNC</t>
+          <t>bot behind the form</t>
         </is>
       </c>
       <c r="H270" s="6" t="inlineStr">
         <is>
-          <t>Bot quotes €69, the form says €74 — resync bot.form_schemas</t>
+          <t>Bot quotes €69, the form says €74. Usually overnight lag — if it is still here after two nights, check Bot - Refresh Form Options</t>
         </is>
       </c>
       <c r="I270" s="7" t="inlineStr">
@@ -20267,12 +20267,12 @@
       </c>
       <c r="G271" s="5" t="inlineStr">
         <is>
-          <t>BOT OUT OF SYNC</t>
+          <t>bot behind the form</t>
         </is>
       </c>
       <c r="H271" s="6" t="inlineStr">
         <is>
-          <t>Bot quotes €62, the form says €67 — resync bot.form_schemas</t>
+          <t>Bot quotes €62, the form says €67. Usually overnight lag — if it is still here after two nights, check Bot - Refresh Form Options</t>
         </is>
       </c>
       <c r="I271" s="7" t="inlineStr">
@@ -20314,12 +20314,12 @@
       </c>
       <c r="G272" s="5" t="inlineStr">
         <is>
-          <t>BOT OUT OF SYNC</t>
+          <t>bot behind the form</t>
         </is>
       </c>
       <c r="H272" s="6" t="inlineStr">
         <is>
-          <t>Bot quotes €55, the form says €60 — resync bot.form_schemas</t>
+          <t>Bot quotes €55, the form says €60. Usually overnight lag — if it is still here after two nights, check Bot - Refresh Form Options</t>
         </is>
       </c>
       <c r="I272" s="7" t="inlineStr">
